--- a/data/Metadata_MeLiDos_RISE.xlsx
+++ b/data/Metadata_MeLiDos_RISE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sp.se\dok\MT\MTk\Arkiv_Gemensamt\FoU-Projektbeskrivningar\FoU-Projekt\EPM MeLiDos\WP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191230BB-051E-4CB9-BC9D-6DDFF422443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{505F962E-CD86-4AA3-9968-948CDC6682F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29190" yWindow="525" windowWidth="25395" windowHeight="16065" xr2:uid="{211FDFF6-B6D5-6945-9CBF-3161228FE565}"/>
   </bookViews>
